--- a/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -82,7 +82,7 @@
   </si>
   <si>
     <t xml:space="preserve">Modèle logique de patientID.
-PatientID représente l’identifiant du patient, en l’occurrence, le matricule INS (NIR ou NIA) du patient. </t>
+Cette métadonnée contient l'identifiant du patient tel que connu par les interlocuteurs prenant part à l'échange. Le matricule INS (NIR ou NIA) du patient doit être utilisé en priorité. À défaut de disponibilité de l'INS, un autre identifiant (ex: IPP du système émetteur) peut être utilisé. </t>
   </si>
   <si>
     <t>Purpose</t>
@@ -261,7 +261,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant du patient, en l’occurrence, le matricule INS du patient tel que défini dans le cadre juridique</t>
+    <t>Identifiant du patient. L'INS du patient tel que défini dans le cadre juridique, est à utiliser prioritairement. À défaut, un autre identifiant (ex : IPP du système émetteur) peut être utilisé.</t>
   </si>
   <si>
     <t>xdmPatientId.CX4</t>
@@ -271,18 +271,18 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l’autorité d’affectation de l’INS utilisé.</t>
-  </si>
-  <si>
-    <t>Cet identifiant, au format HL7 v.2.5 est constitué de trois sous-composants qui prennent les valeurs suivantes.
-|Valeur de Namespace ID (IS)| Valeur de Universal ID (ST)| Valeur de Universal ID type (ID)
-Vide, pas de valeur |OID de l’autorité d’affectation de l’INS utilisé Valeur de Universal ID type (ID) ISO prise dans la liste des OID des autorités d'affectation des INS | ISO</t>
+    <t>Identifiant de l’autorité d’affectation de l'identifiant utilisé.</t>
+  </si>
+  <si>
+    <t>Cet identifiant, au format HL7 v.2.5 est constitué de trois sous-composants qui prennent les valeurs suivantes en fonction du type d'identifiant.
+INS : Valeur de Namespace ID (IS) = Vide, pas de valeur | Valeur de Universal ID (ST) = OID de l’autorité d’affectation de l’INS utilisé, prise dans la liste des OID des autorités d'affectation des INS | Valeur de Universal ID type (ID) = ISO
+Autre identifiant : Valeur de Namespace ID (IS) = Vide, pas de valeur | Valeur de Universal ID (ST) = OID de l’autorité d’affectation dl'identifiant (i.e. l'instituion qui a attribué cet identifiant) | Valeur de Universal ID type (ID) = ISO</t>
   </si>
   <si>
     <t>xdmPatientId.CX5</t>
   </si>
   <si>
-    <t>'NH' pour un maticule INS tel que défini dans le cadre juridique</t>
+    <t>'NH' pour les patients identifiés par leur INS, 'PI' pour les patients identifiés par d'autres identifiants</t>
   </si>
 </sst>
 </file>

--- a/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -257,7 +257,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier
+    <t xml:space="preserve">string {https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/patId|0.1.0}
 </t>
   </si>
   <si>
@@ -597,7 +597,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="7.9765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="65.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmPatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -251,7 +251,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>xdmPatientId.CX1</t>
+    <t>xdmPatientId.cx1</t>
   </si>
   <si>
     <t>1</t>
@@ -264,7 +264,7 @@
     <t>Identifiant du patient. L'INS du patient tel que défini dans le cadre juridique, est à utiliser prioritairement. À défaut, un autre identifiant (ex : IPP du système émetteur) peut être utilisé.</t>
   </si>
   <si>
-    <t>xdmPatientId.CX4</t>
+    <t>xdmPatientId.cx4</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -279,7 +279,7 @@
 Autre identifiant : Valeur de Namespace ID (IS) = Vide, pas de valeur | Valeur de Universal ID (ST) = OID de l’autorité d’affectation dl'identifiant (i.e. l'instituion qui a attribué cet identifiant) | Valeur de Universal ID type (ID) = ISO</t>
   </si>
   <si>
-    <t>xdmPatientId.CX5</t>
+    <t>xdmPatientId.cx5</t>
   </si>
   <si>
     <t>'NH' pour les patients identifiés par leur INS, 'PI' pour les patients identifiés par d'autres identifiants</t>
@@ -587,8 +587,8 @@
   <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="15.03125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="15.03125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.65234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="14.65234375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -618,7 +618,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.03125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="14.65234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
